--- a/results/0916-all/山东丘陵农林区/tech_selected_summary.xlsx
+++ b/results/0916-all/山东丘陵农林区/tech_selected_summary.xlsx
@@ -301,187 +301,187 @@
     <t>邹平县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -508,10 +508,10 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 78885964.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>78885964.68</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -544,7 +544,7 @@
     <t>4R(Right rate)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 149834292.47</t>
+    <t>149834292.47</t>
   </si>
   <si>
     <t>Biochar_beef cattle</t>
@@ -559,7 +559,7 @@
     <t>4R(Right place)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 93839634.64</t>
+    <t>93839634.64</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -613,7 +613,7 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 239043634.12</t>
+    <t>239043634.12</t>
   </si>
   <si>
     <t>Yucca extract_sheep &amp; goat</t>
@@ -661,7 +661,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 99630661.84</t>
+    <t>99630661.84</t>
   </si>
   <si>
     <t>surface crust cover_beef cattle</t>
@@ -685,7 +685,7 @@
     <t>EEF(NI)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 237038315.14</t>
+    <t>237038315.14</t>
   </si>
   <si>
     <t>Frequent removal_beef cattle</t>
@@ -700,19 +700,19 @@
     <t>Mixture additives _pig</t>
   </si>
   <si>
-    <t>总经济成本: 66960523.06</t>
+    <t>66960523.06</t>
   </si>
   <si>
     <t>chemical amendments_pig</t>
   </si>
   <si>
-    <t>总经济成本: 136645922.29</t>
+    <t>136645922.29</t>
   </si>
   <si>
     <t>rolller press_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 8920009.47</t>
+    <t>8920009.47</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -721,7 +721,7 @@
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 14196613.06</t>
+    <t>14196613.06</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -736,55 +736,55 @@
     <t>Feedstock adjustment_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 325383711.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 103140786.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 127281005.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 96150040.24</t>
-  </si>
-  <si>
-    <t>总经济成本: 4246468.09</t>
+    <t>325383711.18</t>
+  </si>
+  <si>
+    <t>103140786.44</t>
+  </si>
+  <si>
+    <t>127281005.46</t>
+  </si>
+  <si>
+    <t>96150040.24</t>
+  </si>
+  <si>
+    <t>4246468.09</t>
   </si>
   <si>
     <t>Physical additives_pig</t>
   </si>
   <si>
-    <t>总经济成本: 94340563.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 302468029.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 130227693.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 265720159.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 15000.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 136870969.93</t>
+    <t>94340563.59</t>
+  </si>
+  <si>
+    <t>302468029.03</t>
+  </si>
+  <si>
+    <t>130227693.96</t>
+  </si>
+  <si>
+    <t>265720159.25</t>
+  </si>
+  <si>
+    <t>15000.00</t>
+  </si>
+  <si>
+    <t>136870969.93</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 582865956.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 141863162.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 36489809.64</t>
-  </si>
-  <si>
-    <t>总经济成本: 377071702.15</t>
+    <t>582865956.77</t>
+  </si>
+  <si>
+    <t>141863162.47</t>
+  </si>
+  <si>
+    <t>36489809.64</t>
+  </si>
+  <si>
+    <t>377071702.15</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
@@ -799,19 +799,19 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 159004133.63</t>
+    <t>159004133.63</t>
   </si>
   <si>
     <t>EEF(CRF)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 104126766.02</t>
-  </si>
-  <si>
-    <t>总经济成本: 60457633.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 10193296.22</t>
+    <t>104126766.02</t>
+  </si>
+  <si>
+    <t>60457633.75</t>
+  </si>
+  <si>
+    <t>10193296.22</t>
   </si>
   <si>
     <t>Chemical amendments_pig</t>
@@ -820,10 +820,10 @@
     <t>EEF(DI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 279736629.43</t>
-  </si>
-  <si>
-    <t>总经济成本: 102115305.42</t>
+    <t>279736629.43</t>
+  </si>
+  <si>
+    <t>102115305.42</t>
   </si>
   <si>
     <t>metal salt_Poultry</t>
@@ -847,82 +847,82 @@
     <t>cover crop (non-leguminous)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 288413274.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 61073677.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 307362517.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 297045897.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 106343045.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 168605281.17</t>
-  </si>
-  <si>
-    <t>总经济成本: -1242917.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 145137367.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 168148951.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 65591498.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 156575608.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 180025280.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 49480200.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 99401248.53</t>
-  </si>
-  <si>
-    <t>总经济成本: 98847301.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 230352171.58</t>
+    <t>288413274.12</t>
+  </si>
+  <si>
+    <t>61073677.84</t>
+  </si>
+  <si>
+    <t>307362517.59</t>
+  </si>
+  <si>
+    <t>297045897.20</t>
+  </si>
+  <si>
+    <t>106343045.25</t>
+  </si>
+  <si>
+    <t>168605281.17</t>
+  </si>
+  <si>
+    <t>-1242917.50</t>
+  </si>
+  <si>
+    <t>145137367.44</t>
+  </si>
+  <si>
+    <t>168148951.67</t>
+  </si>
+  <si>
+    <t>65591498.84</t>
+  </si>
+  <si>
+    <t>156575608.39</t>
+  </si>
+  <si>
+    <t>180025280.70</t>
+  </si>
+  <si>
+    <t>49480200.04</t>
+  </si>
+  <si>
+    <t>99401248.53</t>
+  </si>
+  <si>
+    <t>98847301.56</t>
+  </si>
+  <si>
+    <t>230352171.58</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
   </si>
   <si>
-    <t>总经济成本: 157952401.58</t>
+    <t>157952401.58</t>
   </si>
   <si>
     <t>incorporation_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 157800187.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 524376782.24</t>
-  </si>
-  <si>
-    <t>总经济成本: 201520740.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 248710116.30</t>
-  </si>
-  <si>
-    <t>总经济成本: 43860579.45</t>
+    <t>157800187.46</t>
+  </si>
+  <si>
+    <t>524376782.24</t>
+  </si>
+  <si>
+    <t>201520740.95</t>
+  </si>
+  <si>
+    <t>248710116.30</t>
+  </si>
+  <si>
+    <t>43860579.45</t>
   </si>
   <si>
     <t>Feedstock adjustment_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 95364933.72</t>
+    <t>95364933.72</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
@@ -931,37 +931,37 @@
     <t>4R(Right place)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 296595489.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 257272679.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 228763126.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 314489201.79</t>
+    <t>296595489.25</t>
+  </si>
+  <si>
+    <t>257272679.40</t>
+  </si>
+  <si>
+    <t>228763126.84</t>
+  </si>
+  <si>
+    <t>314489201.79</t>
   </si>
   <si>
     <t>Urease Inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 88491905.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 123365621.06</t>
-  </si>
-  <si>
-    <t>总经济成本: 374589807.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 1874774.29</t>
-  </si>
-  <si>
-    <t>总经济成本: 34160988.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 262617535.06</t>
+    <t>88491905.84</t>
+  </si>
+  <si>
+    <t>123365621.06</t>
+  </si>
+  <si>
+    <t>374589807.87</t>
+  </si>
+  <si>
+    <t>1874774.29</t>
+  </si>
+  <si>
+    <t>34160988.13</t>
+  </si>
+  <si>
+    <t>262617535.06</t>
   </si>
 </sst>
 </file>
